--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,20 +482,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,164 +513,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>54</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CONMEBOL</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Japon</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>81</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AFC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>234</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>papulandia</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>666</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>conme</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3232</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>etesechpotaxie</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>spiderboys</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>67</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>conmespiderboys</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -1,34 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7E44F9-C294-46C9-BFE0-E2E3B93F08BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4770" yWindow="8160" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>pais</t>
+  </si>
+  <si>
+    <t>grupo</t>
+  </si>
+  <si>
+    <t>prefijo</t>
+  </si>
+  <si>
+    <t>confederacion</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +76,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,129 +378,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pais</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>prefijo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>confederacion</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>puntos</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>gf</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>gc</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>pj</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>595</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CON</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Estados Unidos</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>UEFA</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -1,63 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7E44F9-C294-46C9-BFE0-E2E3B93F08BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="4770" yWindow="8160" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>pais</t>
-  </si>
-  <si>
-    <t>grupo</t>
-  </si>
-  <si>
-    <t>prefijo</t>
-  </si>
-  <si>
-    <t>confederacion</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -76,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -378,28 +408,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="15.140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prefijo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>confederacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>uefa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>212</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CONMEBOL</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -451,32 +451,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>uefa</t>
+          <t>CONMEBOL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>212</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -1,34 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDFC774-B2C2-4A56-B0A4-4C0D47734521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1365" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>pais</t>
+  </si>
+  <si>
+    <t>grupo</t>
+  </si>
+  <si>
+    <t>prefijo</t>
+  </si>
+  <si>
+    <t>confederacion</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +76,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,89 +378,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pais</t>
-        </is>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>prefijo</t>
-        </is>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>confederacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>595</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CONMEBOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>47</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CONMEBOL</t>
-        </is>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDFC774-B2C2-4A56-B0A4-4C0D47734521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F21FB-5E50-4FE0-B84C-54D9BD401AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13680" yWindow="2580" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F21FB-5E50-4FE0-B84C-54D9BD401AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107CB16D-1FA2-4B65-AF71-DF649915FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13680" yWindow="2580" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14025" yWindow="2925" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="119">
   <si>
     <t>id</t>
   </si>
@@ -40,6 +40,348 @@
   </si>
   <si>
     <t>confederacion</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>CONCACAF</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>CAF</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
+  </si>
+  <si>
+    <t>AFC</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Chequia</t>
+  </si>
+  <si>
+    <t>UEFA</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Bosnia y Herzegovina</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>Suiza</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>CONMEBOL</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Marruecos</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Haití</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Escocia</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Curazao</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>Costa de Marfil</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Japón</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>Túnez</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Egipto</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Irán</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>Nueva Zelanda</t>
+  </si>
+  <si>
+    <t>OFC</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Arabia Saudita</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Argelia</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Jordania</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>Congo DR</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Uzbekistán</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>Croacia</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>Panamá</t>
   </si>
 </sst>
 </file>
@@ -379,8 +721,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -399,6 +744,822 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>52</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>420</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>387</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>974</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>212</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>509</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>595</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>599</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20">
+        <v>225</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21">
+        <v>593</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25">
+        <v>216</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28">
+        <v>98</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31">
+        <v>238</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32">
+        <v>966</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33">
+        <v>598</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35">
+        <v>221</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36">
+        <v>964</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37">
+        <v>47</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39">
+        <v>213</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40">
+        <v>43</v>
+      </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41">
+        <v>962</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42">
+        <v>351</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43">
+        <v>243</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44">
+        <v>998</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45">
+        <v>57</v>
+      </c>
+      <c r="E45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46">
+        <v>44</v>
+      </c>
+      <c r="E46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47">
+        <v>385</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48">
+        <v>233</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49">
+        <v>507</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/equipos.xlsx
+++ b/data/equipos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TP ALGO 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1C766A-9B56-44EC-97A9-D70CD1D911A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107CB16D-1FA2-4B65-AF71-DF649915FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="3750" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14025" yWindow="2925" windowWidth="14490" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="119">
   <si>
     <t>id</t>
   </si>
@@ -40,6 +40,348 @@
   </si>
   <si>
     <t>confederacion</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>CONCACAF</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>CAF</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
+  </si>
+  <si>
+    <t>AFC</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Chequia</t>
+  </si>
+  <si>
+    <t>UEFA</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Bosnia y Herzegovina</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>Suiza</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>CONMEBOL</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Marruecos</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Haití</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Escocia</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Curazao</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>Costa de Marfil</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Japón</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>Túnez</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Egipto</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Irán</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>Nueva Zelanda</t>
+  </si>
+  <si>
+    <t>OFC</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Arabia Saudita</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Argelia</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Jordania</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>Congo DR</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Uzbekistán</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>Croacia</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>Panamá</t>
   </si>
 </sst>
 </file>
@@ -379,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
@@ -402,6 +744,822 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>52</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>420</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>387</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>974</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>212</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>509</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>595</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>599</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20">
+        <v>225</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21">
+        <v>593</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25">
+        <v>216</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28">
+        <v>98</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31">
+        <v>238</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32">
+        <v>966</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33">
+        <v>598</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35">
+        <v>221</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36">
+        <v>964</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37">
+        <v>47</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39">
+        <v>213</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40">
+        <v>43</v>
+      </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41">
+        <v>962</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42">
+        <v>351</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43">
+        <v>243</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44">
+        <v>998</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45">
+        <v>57</v>
+      </c>
+      <c r="E45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46">
+        <v>44</v>
+      </c>
+      <c r="E46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47">
+        <v>385</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48">
+        <v>233</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49">
+        <v>507</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
